--- a/regional_sales_reports/regional_sales_report.xlsx
+++ b/regional_sales_reports/regional_sales_report.xlsx
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>46187.67546296296</v>
+        <v>46187.6928587963</v>
       </c>
     </row>
     <row r="5"/>

--- a/regional_sales_reports/regional_sales_report.xlsx
+++ b/regional_sales_reports/regional_sales_report.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>46193.47876157407</v>
+        <v>46193.480625</v>
       </c>
     </row>
     <row r="5"/>

--- a/regional_sales_reports/regional_sales_report.xlsx
+++ b/regional_sales_reports/regional_sales_report.xlsx
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>46193.480625</v>
+        <v>46193.50148148148</v>
       </c>
     </row>
     <row r="5"/>
